--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$6</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,6 +332,9 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -471,6 +477,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -814,7 +835,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -917,7 +938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>82</v>
       </c>
@@ -1020,7 +1041,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>89</v>
       </c>
@@ -1123,7 +1144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1247,7 +1268,7 @@
         <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1256,13 +1277,13 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1325,13 +1346,31 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>101</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK6">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI5">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -315,6 +315,9 @@
     <t>Extension.url</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">uri
 </t>
   </si>
@@ -332,9 +335,6 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -1144,7 +1144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -1172,16 +1172,16 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1246,15 +1246,15 @@
         <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1268,7 +1268,7 @@
         <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1334,7 +1334,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1349,7 +1349,7 @@
         <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-patient-modified.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
